--- a/Assessment Questions/AIE/BDF-117/PYSPARK FOUNDATION/Resilient distributed datasets (RDD)/Resilient distributed datasets (RDD).xlsx
+++ b/Assessment Questions/AIE/BDF-117/PYSPARK FOUNDATION/Resilient distributed datasets (RDD)/Resilient distributed datasets (RDD).xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>RDD_ID,RDD_Name,Operation_Type,Operation_Name,Input_Partitions,Output_Partitions,Input_Records,Output_Records,Execution_Time_Sec,Memory_MB,Shuffle_Read_MB,Shuffle_Write_MB,Lineage_Depth,Narrow_Dependencies,Wide_Dependencies,Partition_Size_MB,Data_Locality_Pct,Fault_Tolerance_Mechanism,Checkpoint_Used,Cache_Level,Task_Failed_Count,Success_Status,Recovery_Time_Sec</t>
-  </si>
-  <si>
-    <t>RDD-001,TextFile_RDD,Create,textFile,4,4,10000000,10000000,8,1024,0,0,1,0,0,256,95,Recompute,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-002,Filtered_RDD,Transformation,filter,4,4,10000000,5000000,12,1024,0,0,2,1,0,256,94,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-003,Mapped_RDD,Transformation,map,4,4,10000000,10000000,15,1024,0,0,3,1,0,256,93,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-004,FlatMapped_RDD,Transformation,flatMap,4,12,5000000,15000000,25,1536,0,0,4,1,0,128,92,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-005,Reduced_RDD,Action,reduce,4,1,10000000,1,22,2048,1280,0,5,0,1,1024,85,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-006,Grouped_RDD,Transformation,groupByKey,12,12,12000000,8000000,45,3072,2560,1280,6,0,1,256,78,Lineage,No,NONE,2,Partial,45</t>
-  </si>
-  <si>
-    <t>RDD-007,Joined_RDD,Transformation,join,16,16,20000000,15000000,120,4096,5120,3840,7,0,1,256,72,Lineage,Yes,MEMORY_ONLY,3,Success,120</t>
-  </si>
-  <si>
-    <t>RDD-008,Aggregated_RDD,Transformation,reduceByKey,12,8,12000000,3000000,28,2048,1920,960,5,0,1,384,82,Lineage,No,MEMORY_ONLY,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-009,Union_RDD,Transformation,union,8,8,25000000,25000000,18,1536,0,0,4,2,0,512,88,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-010,Sorted_RDD,Transformation,sortByKey,8,8,18000000,18000000,68,3072,3840,3840,6,0,1,256,70,Lineage,No,MEMORY_AND_DISK,1,Success,68</t>
-  </si>
-  <si>
-    <t>RDD-011,Distinct_RDD,Transformation,distinct,16,16,12000000,6000000,42,2560,2560,1280,5,0,1,256,75,Lineage,No,NONE,2,Success,42</t>
-  </si>
-  <si>
-    <t>RDD-012,Sampled_RDD,Transformation,sample,4,4,10000000,1000000,8,512,0,0,3,1,0,256,90,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-013,Collected_RDD,Action,collect,8,1,8000000,8000000,35,4096,0,0,4,0,1,1024,80,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-014,Cached_RDD,Transformation,cache,8,8,15000000,15000000,5,2048,0,0,5,1,0,256,92,Checkpoint,Yes,MEMORY_ONLY,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-015,Persisted_RDD,Transformation,persist,8,8,20000000,20000000,8,4096,0,0,6,1,0,256,89,Checkpoint,Yes,MEMORY_AND_DISK,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-016,CoGroup_RDD,Transformation,cogroup,32,32,22000000,18000000,85,8192,7680,5120,8,0,2,128,65,Lineage,No,NONE,5,Partial,85</t>
-  </si>
-  <si>
-    <t>RDD-017,Partitioned_RDD,Transformation,partitionBy,8,32,10000000,10000000,20,2048,0,1280,4,0,1,64,88,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-018,MapPartitions_RDD,Transformation,mapPartitions,8,8,10000000,10000000,20,2048,0,0,3,1,0,256,91,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-019,Zip_RDD,Transformation,zip,4,4,5000000,5000000,15,1024,0,0,4,1,0,512,85,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-020,Intersection_RDD,Transformation,intersection,8,8,8000000,4000000,35,2048,1280,1280,5,0,1,256,72,Lineage,No,NONE,1,Success,35</t>
-  </si>
-  <si>
-    <t>RDD-021,Cartesian_RDD,Transformation,cartesian,4,16,5000,25000000,180,8192,0,0,3,0,1,2,60,Lineage,No,NONE,4,Partial,180</t>
-  </si>
-  <si>
-    <t>RDD-022,Coalesced_RDD,Transformation,coalesce,16,4,20000000,20000000,12,2048,0,0,4,1,0,512,95,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-023,Repartitioned_RDD,Transformation,repartition,4,16,10000000,10000000,25,2048,0,1280,4,0,1,128,88,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-024,First_Action,Action,first,4,1,5000000,1,1,256,0,0,5,0,1,1024,90,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-025,Take_Action,Action,take,4,1,5000000,100,2,256,0,0,5,0,1,1024,92,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-026,Count_Action,Action,count,4,1,10000000,1,8,512,0,0,4,0,1,1024,95,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-027,Save_RDD,Action,saveAsTextFile,8,8,15000000,15000000,52,2048,0,0,4,0,1,256,85,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-028,Foreach_Action,Action,foreach,8,0,5000000,0,15,1024,0,0,4,0,1,256,88,Lineage,No,NONE,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-029,Checkpointed_RDD,Transformation,checkpoint,16,16,25000000,25000000,45,4096,0,0,12,1,0,256,82,Checkpoint,Yes,MEMORY_ONLY,0,Success,0</t>
-  </si>
-  <si>
-    <t>RDD-030,Recovered_RDD,Fault_Tolerance,recover,8,8,10000000,10000000,25,2048,0,0,2,0,0,256,95,Lineage,No,NONE,2,Success,25</t>
-  </si>
-  <si>
-    <t>Q.No,Question,RDD_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is RDD (Resilient Distributed Dataset)? Explain its key characteristics using the dataset.","RDD Definition","Analyze RDD properties from dataset","RDDs are fault-tolerant, immutable, distributed collections. Characteristics: Partitioned (4-32 partitions), Immutable (operations create new RDDs), Resilient (lineage depth 1-12)","RDDs are fundamental Spark abstraction; provide fault tolerance via lineage"</t>
-  </si>
-  <si>
-    <t>2,"What are the different ways to create RDDs? Identify creation operations from dataset.","RDD Creation","Filter Operation_Type='Create'","Creation: textFile (RDD-001). Also parallelize, from external sources. Creates base RDD with lineage depth 1","RDDs created from external data or parallelizing existing collections"</t>
-  </si>
-  <si>
-    <t>3,"What are RDD Transformations? Explain lazy evaluation using dataset examples.","Transformations","Filter Operation_Type='Transformation'","Transformations: filter, map, flatMap, groupByKey, join, reduceByKey. Lazy evaluation: execution triggered only by actions (22-52s)","Transformations are lazy; build DAG but don't execute immediately"</t>
-  </si>
-  <si>
-    <t>4,"What are RDD Actions? How do they trigger execution? Analyze from dataset.","Actions","Filter Operation_Type='Action'","Actions: reduce (22s), collect (35s), count (8s), take (2s), save (52s), first (1s). Trigger execution and return results to driver","Actions force computation; result can be collected or saved"</t>
-  </si>
-  <si>
-    <t>5,"What is Lineage in RDD? Analyze lineage depth across different operations.","RDD Lineage","Analyze Lineage_Depth column","Lineage depth: 1 (creation) → 5-7 (complex operations) → 12 (checkpointed). Deeper lineage = more transformations in DAG","Lineage tracks transformation history; enables fault tolerance"</t>
-  </si>
-  <si>
-    <t>6,"What is the difference between Narrow and Wide dependencies? Identify from dataset.","Dependencies","Analyze Narrow_Dependencies vs Wide_Dependencies","Narrow (filter, map): 1 parent partition → 1 child (no shuffle). Wide (groupBy, join): multiple parents → child (shuffle required)","Narrow dependencies are faster; wide require shuffle"</t>
-  </si>
-  <si>
-    <t>7,"What is Data Locality in RDD? Analyze locality percentages across operations.","Data Locality","Analyze Data_Locality_Pct column","Data locality: 60-95%. Best: textFile (95%), filter (94%), coalesce (95%). Worst: cartesian (60%), cogroup (65%), join (72%)","High locality (moving computation to data) improves performance"</t>
-  </si>
-  <si>
-    <t>8,"What are Partitions in RDD? How does partition count affect performance?","Partitioning","Analyze Input_Partitions, Output_Partitions, Partition_Size_MB","Partitions: 4-32. Optimal partition size: 128-256 MB. coalesce reduces partitions (16→4), repartition increases (4→16)","Right partition count balances parallelism and overhead"</t>
-  </si>
-  <si>
-    <t>9,"What is Fault Tolerance in RDD? How is it achieved? Analyze from dataset.","Fault Tolerance","Analyze Fault_Tolerance_Mechanism, Recovery_Time_Sec","Fault tolerance via: Lineage (recompute), Checkpoint (save to storage). Recovery time: 25-180 sec depending on lineage depth","RDDs recover lost partitions by recomputing from lineage or checkpoint"</t>
-  </si>
-  <si>
-    <t>10,"What is Caching/Persistence? How does it improve performance?","Caching","Filter Cache_Level != 'NONE'","Cached RDDs: reduceByKey (MEMORY_ONLY), join (MEMORY_ONLY), sortByKey (MEMORY_AND_DISK). Execution time 5-8s vs 28-68s uncached","Cache frequently used RDDs to avoid recomputation"</t>
-  </si>
-  <si>
-    <t>11,"What is Checkpointing? When should it be used? Analyze from dataset.","Checkpointing","Filter Checkpoint_Used='Yes'","Checkpoint used: join (lineage 7), cached RDD (lineage 5-6), checkpointed RDD (lineage 12). Breaks long lineage chains","Use checkpoint for long lineages (depth &gt;10) or iterative algorithms"</t>
-  </si>
-  <si>
-    <t>12,"What is the difference between reduceByKey and groupByKey? Analyze performance.","reduceByKey vs groupByKey","Compare RDD-008 (reduceByKey) vs RDD-006 (groupByKey)","reduceByKey: 28s, 1.9GB shuffle, 3M output; groupByKey: 45s, 2.5GB shuffle, 8M output. reduceByKey 38% faster","reduceByKey does map-side aggregation; groupByKey does not"</t>
-  </si>
-  <si>
-    <t>13,"What is the difference between coalesce and repartition? Analyze from dataset.","coalesce vs repartition","Compare RDD-022 (coalesce) vs RDD-023 (repartition)","coalesce: reduces partitions without shuffle (12s); repartition: increases with shuffle (25s). coalesce faster for decreasing","Use coalesce to reduce partitions; repartition to increase"</t>
-  </si>
-  <si>
-    <t>14,"What is the impact of shuffle on performance? Analyze shuffle metrics.","Shuffle Impact","Analyze Shuffle_Read_MB, Shuffle_Write_MB","Shuffle-heavy ops: join (5.1GB read, 3.8GB write, 120s), cogroup (7.7GB read, 5.1GB write, 85s). Shuffle increases execution time","Shuffle is expensive; minimize wide transformations"</t>
-  </si>
-  <si>
-    <t>15,"What are the most expensive RDD operations? Identify top by execution time.","Performance Analysis","Sort by Execution_Time_Sec descending","Cartesian (180s), Join (120s), Cogroup (85s), Sort (68s). All are wide transformations with shuffle","Avoid cartesian; optimize joins with broadcast for small tables"</t>
-  </si>
-  <si>
-    <t>16,"What is the difference between map and flatMap? Analyze from dataset.","map vs flatMap","Compare RDD-003 (map) vs RDD-004 (flatMap)","map: 15s, 10M→10M (1:1); flatMap: 25s, 5M→15M (1:3). flatMap expands records","Use flatMap for 1-to-many transformations; map for 1-to-1"</t>
-  </si>
-  <si>
-    <t>17,"What are the different cache levels? Analyze from dataset.","Cache Levels","Analyze Cache_Level column","Levels: MEMORY_ONLY (fastest), MEMORY_AND_DISK (fallback), NONE (no cache). Cache reduces execution 3-5x for repeated operations","Choose cache level based on memory availability"</t>
-  </si>
-  <si>
-    <t>18,"What is data skew? How does it affect RDD operations? Analyze from dataset.","Data Skew","Analyze Task_Failed_Count, Success_Status","Skewed ops: cogroup (5 failures), cartesian (4 failures), join (3 failures). Causes task failures and partial success","Data skew causes uneven partition sizes; use salting or AQE"</t>
-  </si>
-  <si>
-    <t>19,"What is the RDD lineage recovery process? Analyze recovery time.","Lineage Recovery","Analyze Recovered_RDD (RDD-030)","Recovered RDD: lineage depth 2, recovery time 25s. Recomputes from parent RDD using lineage","Lineage enables efficient recovery; checkpoint reduces recovery time"</t>
-  </si>
-  <si>
-    <t>20,"Create an RDD optimization checklist based on dataset metrics.","Optimization Guide","Summarize best practices","1. Use reduceByKey over groupByKey (38% faster) 2. Cache frequently used RDDs (3-5x faster) 3. Checkpoint long lineages (depth&gt;10) 4. Use coalesce to reduce partitions 5. Optimize partition size (128-256MB)","Optimization significantly improves RDD performance"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,983 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RDD_ID,RDD_Name,Operation_Type,Operation_Name,Input_Partitions,Output_Partitions,Input_Records,Output_Records,Execution_Time_Sec,Memory_MB,Shuffle_Read_MB,Shuffle_Write_MB,Lineage_Depth,Narrow_Dependencies,Wide_Dependencies,Partition_Size_MB,Data_Locality_Pct,Fault_Tolerance_Mechanism,Checkpoint_Used,Cache_Level,Task_Failed_Count,Success_Status,Recovery_Time_Sec</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>RDD-001,TextFile_RDD,Create,textFile,4,4,10000000,10000000,8,1024,0,0,1,0,0,256,95,Recompute,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RDD-002,Filtered_RDD,Transformation,filter,4,4,10000000,5000000,12,1024,0,0,2,1,0,256,94,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>RDD-003,Mapped_RDD,Transformation,map,4,4,10000000,10000000,15,1024,0,0,3,1,0,256,93,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>RDD-004,FlatMapped_RDD,Transformation,flatMap,4,12,5000000,15000000,25,1536,0,0,4,1,0,128,92,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>RDD-005,Reduced_RDD,Action,reduce,4,1,10000000,1,22,2048,1280,0,5,0,1,1024,85,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>RDD-006,Grouped_RDD,Transformation,groupByKey,12,12,12000000,8000000,45,3072,2560,1280,6,0,1,256,78,Lineage,No,NONE,2,Partial,45</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>RDD-007,Joined_RDD,Transformation,join,16,16,20000000,15000000,120,4096,5120,3840,7,0,1,256,72,Lineage,Yes,MEMORY_ONLY,3,Success,120</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>RDD-008,Aggregated_RDD,Transformation,reduceByKey,12,8,12000000,3000000,28,2048,1920,960,5,0,1,384,82,Lineage,No,MEMORY_ONLY,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>RDD-009,Union_RDD,Transformation,union,8,8,25000000,25000000,18,1536,0,0,4,2,0,512,88,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>RDD-010,Sorted_RDD,Transformation,sortByKey,8,8,18000000,18000000,68,3072,3840,3840,6,0,1,256,70,Lineage,No,MEMORY_AND_DISK,1,Success,68</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>RDD-011,Distinct_RDD,Transformation,distinct,16,16,12000000,6000000,42,2560,2560,1280,5,0,1,256,75,Lineage,No,NONE,2,Success,42</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>RDD-012,Sampled_RDD,Transformation,sample,4,4,10000000,1000000,8,512,0,0,3,1,0,256,90,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>RDD-013,Collected_RDD,Action,collect,8,1,8000000,8000000,35,4096,0,0,4,0,1,1024,80,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>RDD-014,Cached_RDD,Transformation,cache,8,8,15000000,15000000,5,2048,0,0,5,1,0,256,92,Checkpoint,Yes,MEMORY_ONLY,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>RDD-015,Persisted_RDD,Transformation,persist,8,8,20000000,20000000,8,4096,0,0,6,1,0,256,89,Checkpoint,Yes,MEMORY_AND_DISK,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>RDD-016,CoGroup_RDD,Transformation,cogroup,32,32,22000000,18000000,85,8192,7680,5120,8,0,2,128,65,Lineage,No,NONE,5,Partial,85</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>RDD-017,Partitioned_RDD,Transformation,partitionBy,8,32,10000000,10000000,20,2048,0,1280,4,0,1,64,88,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>RDD-018,MapPartitions_RDD,Transformation,mapPartitions,8,8,10000000,10000000,20,2048,0,0,3,1,0,256,91,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>RDD-019,Zip_RDD,Transformation,zip,4,4,5000000,5000000,15,1024,0,0,4,1,0,512,85,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>RDD-020,Intersection_RDD,Transformation,intersection,8,8,8000000,4000000,35,2048,1280,1280,5,0,1,256,72,Lineage,No,NONE,1,Success,35</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>RDD-021,Cartesian_RDD,Transformation,cartesian,4,16,5000,25000000,180,8192,0,0,3,0,1,2,60,Lineage,No,NONE,4,Partial,180</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>RDD-022,Coalesced_RDD,Transformation,coalesce,16,4,20000000,20000000,12,2048,0,0,4,1,0,512,95,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>RDD-023,Repartitioned_RDD,Transformation,repartition,4,16,10000000,10000000,25,2048,0,1280,4,0,1,128,88,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>RDD-024,First_Action,Action,first,4,1,5000000,1,1,256,0,0,5,0,1,1024,90,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>RDD-025,Take_Action,Action,take,4,1,5000000,100,2,256,0,0,5,0,1,1024,92,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>RDD-026,Count_Action,Action,count,4,1,10000000,1,8,512,0,0,4,0,1,1024,95,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>RDD-027,Save_RDD,Action,saveAsTextFile,8,8,15000000,15000000,52,2048,0,0,4,0,1,256,85,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>RDD-028,Foreach_Action,Action,foreach,8,0,5000000,0,15,1024,0,0,4,0,1,256,88,Lineage,No,NONE,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>RDD-029,Checkpointed_RDD,Transformation,checkpoint,16,16,25000000,25000000,45,4096,0,0,12,1,0,256,82,Checkpoint,Yes,MEMORY_ONLY,0,Success,0</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>RDD-030,Recovered_RDD,Fault_Tolerance,recover,8,8,10000000,10000000,25,2048,0,0,2,0,0,256,95,Lineage,No,NONE,2,Success,25</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is RDD (Resilient Distributed Dataset)? Explain its key characteristics using the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze RDD properties from dataset | RDDs are fault-tolerant, immutable, distributed collections. Characteristics: Partitioned (4-32 partitions), Immutable (operations create new RDDs), Resilient (lineage depth 1-12)</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>RDDs are fundamental Spark abstraction; provide fault tolerance via lineage</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What are the different ways to create RDDs? Identify creation operations from dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Filter Operation_Type='Create' | Creation: textFile (RDD-001). Also parallelize, from external sources. Creates base RDD with lineage depth 1</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>RDDs created from external data or parallelizing existing collections</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What are RDD Transformations? Explain lazy evaluation using dataset examples.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Filter Operation_Type='Transformation' | Transformations: filter, map, flatMap, groupByKey, join, reduceByKey. Lazy evaluation: execution triggered only by actions (22-52s)</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Transformations are lazy; build DAG but don't execute immediately</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What are RDD Actions? How do they trigger execution? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Filter Operation_Type='Action' | Actions: reduce (22s), collect (35s), count (8s), take (2s), save (52s), first (1s). Trigger execution and return results to driver</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Actions force computation; result can be collected or saved</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is Lineage in RDD? Analyze lineage depth across different operations.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Lineage_Depth column | Lineage depth: 1 (creation) → 5-7 (complex operations) → 12 (checkpointed). Deeper lineage = more transformations in DAG</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Lineage tracks transformation history; enables fault tolerance</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between Narrow and Wide dependencies? Identify from dataset.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Narrow_Dependencies vs Wide_Dependencies | Narrow (filter, map): 1 parent partition → 1 child (no shuffle). Wide (groupBy, join): multiple parents → child (shuffle required)</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Narrow dependencies are faster; wide require shuffle</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What is Data Locality in RDD? Analyze locality percentages across operations.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Data_Locality_Pct column | Data locality: 60-95%. Best: textFile (95%), filter (94%), coalesce (95%). Worst: cartesian (60%), cogroup (65%), join (72%)</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>High locality (moving computation to data) improves performance</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What are Partitions in RDD? How does partition count affect performance?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Input_Partitions, Output_Partitions, Partition_Size_MB | Partitions: 4-32. Optimal partition size: 128-256 MB. coalesce reduces partitions (16→4), repartition increases (4→16)</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Right partition count balances parallelism and overhead</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What is Fault Tolerance in RDD? How is it achieved? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Fault_Tolerance_Mechanism, Recovery_Time_Sec | Fault tolerance via: Lineage (recompute), Checkpoint (save to storage). Recovery time: 25-180 sec depending on lineage depth</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>RDDs recover lost partitions by recomputing from lineage or checkpoint</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What is Caching/Persistence? How does it improve performance?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Filter Cache_Level != 'NONE' | Cached RDDs: reduceByKey (MEMORY_ONLY), join (MEMORY_ONLY), sortByKey (MEMORY_AND_DISK). Execution time 5-8s vs 28-68s uncached</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Cache frequently used RDDs to avoid recomputation</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What is Checkpointing? When should it be used? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Filter Checkpoint_Used='Yes' | Checkpoint used: join (lineage 7), cached RDD (lineage 5-6), checkpointed RDD (lineage 12). Breaks long lineage chains</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Use checkpoint for long lineages (depth &gt;10) or iterative algorithms</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between reduceByKey and groupByKey? Analyze performance.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Compare RDD-008 (reduceByKey) vs RDD-006 (groupByKey) | reduceByKey: 28s, 1.9GB shuffle, 3M output; groupByKey: 45s, 2.5GB shuffle, 8M output. reduceByKey 38% faster</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>reduceByKey does map-side aggregation; groupByKey does not</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between coalesce and repartition? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Compare RDD-022 (coalesce) vs RDD-023 (repartition) | coalesce: reduces partitions without shuffle (12s); repartition: increases with shuffle (25s). coalesce faster for decreasing</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>Use coalesce to reduce partitions; repartition to increase</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What is the impact of shuffle on performance? Analyze shuffle metrics.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Shuffle_Read_MB, Shuffle_Write_MB | Shuffle-heavy ops: join (5.1GB read, 3.8GB write, 120s), cogroup (7.7GB read, 5.1GB write, 85s). Shuffle increases execution time</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Shuffle is expensive; minimize wide transformations</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What are the most expensive RDD operations? Identify top by execution time.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Sort by Execution_Time_Sec descending | Cartesian (180s), Join (120s), Cogroup (85s), Sort (68s). All are wide transformations with shuffle</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Avoid cartesian; optimize joins with broadcast for small tables</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between map and flatMap? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Compare RDD-003 (map) vs RDD-004 (flatMap) | map: 15s, 10M→10M (1:1); flatMap: 25s, 5M→15M (1:3). flatMap expands records</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Use flatMap for 1-to-many transformations; map for 1-to-1</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What are the different cache levels? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Cache_Level column | Levels: MEMORY_ONLY (fastest), MEMORY_AND_DISK (fallback), NONE (no cache). Cache reduces execution 3-5x for repeated operations</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Choose cache level based on memory availability</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is data skew? How does it affect RDD operations? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Task_Failed_Count, Success_Status | Skewed ops: cogroup (5 failures), cartesian (4 failures), join (3 failures). Causes task failures and partial success</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Data skew causes uneven partition sizes; use salting or AQE</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What is the RDD lineage recovery process? Analyze recovery time.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Recovered_RDD (RDD-030) | Recovered RDD: lineage depth 2, recovery time 25s. Recomputes from parent RDD using lineage</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Lineage enables efficient recovery; checkpoint reduces recovery time</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Resilient distributed datasets (RDD)</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create an RDD optimization checklist based on dataset metrics.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Summarize best practices | 1. Use reduceByKey over groupByKey (38% faster) 2. Cache frequently used RDDs (3-5x faster) 3. Checkpoint long lineages (depth&gt;10) 4. Use coalesce to reduce partitions 5. Optimize partition size (128-256MB)</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Optimization significantly improves RDD performance</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>